--- a/AfterToken/Configs/GameConfig/Datas/companionbark.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/companionbark.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,6 +890,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>70</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chat_busy</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>companion.bark.chat_busy.1</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>71</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>chat_busy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>companion.bark.chat_busy.2</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/companionbark.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/companionbark.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,279 @@
         <v>3</v>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>80</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>quiet_ack</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>companion.bark.quiet_ack</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>90</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>danger_alert</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>companion.bark.danger_alert.1</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>91</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>danger_alert</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>companion.bark.danger_alert.2</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>100</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>combat_end</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_end.1</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>101</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>combat_end</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_end.2</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>110</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>combat_dir_front</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_dir.front</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>111</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>combat_dir_back</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_dir.back</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>112</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>combat_dir_left</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_dir.left</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>113</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>combat_dir_right</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_dir.right</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>114</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>combat_dir_front_left</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_dir.front_left</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>115</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>combat_dir_front_right</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_dir.front_right</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>116</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>combat_dir_back_left</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_dir.back_left</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>117</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>combat_dir_back_right</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>companion.bark.combat_dir.back_right</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/companionbark.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/companionbark.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>cooldown</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>minTier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +484,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,6 +521,11 @@
           <t>单键冷却s(0=不限)</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>最低好感档位(1-4)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="n">
@@ -532,6 +547,9 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -552,6 +570,9 @@
       </c>
       <c r="F5" t="n">
         <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -574,6 +595,9 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -595,6 +619,9 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -616,6 +643,9 @@
       <c r="F8" t="n">
         <v>4</v>
       </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -637,6 +667,9 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -658,6 +691,9 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -679,6 +715,9 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -700,6 +739,9 @@
       <c r="F12" t="n">
         <v>2</v>
       </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -721,6 +763,9 @@
       <c r="F13" t="n">
         <v>2</v>
       </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
@@ -742,6 +787,9 @@
       <c r="F14" t="n">
         <v>2</v>
       </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
@@ -763,6 +811,9 @@
       <c r="F15" t="n">
         <v>2</v>
       </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
@@ -784,6 +835,9 @@
       <c r="F16" t="n">
         <v>2</v>
       </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
@@ -805,6 +859,9 @@
       <c r="F17" t="n">
         <v>0</v>
       </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
@@ -826,6 +883,9 @@
       <c r="F18" t="n">
         <v>0</v>
       </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
@@ -847,6 +907,9 @@
       <c r="F19" t="n">
         <v>8</v>
       </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
@@ -868,6 +931,9 @@
       <c r="F20" t="n">
         <v>6</v>
       </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
@@ -889,6 +955,9 @@
       <c r="F21" t="n">
         <v>0</v>
       </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
@@ -910,6 +979,9 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
@@ -931,6 +1003,9 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
@@ -952,6 +1027,9 @@
       <c r="F24" t="n">
         <v>0</v>
       </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
@@ -973,6 +1051,9 @@
       <c r="F25" t="n">
         <v>8</v>
       </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
@@ -994,6 +1075,9 @@
       <c r="F26" t="n">
         <v>8</v>
       </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
@@ -1015,6 +1099,9 @@
       <c r="F27" t="n">
         <v>6</v>
       </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
@@ -1036,6 +1123,9 @@
       <c r="F28" t="n">
         <v>6</v>
       </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
@@ -1057,6 +1147,9 @@
       <c r="F29" t="n">
         <v>10</v>
       </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
@@ -1078,6 +1171,9 @@
       <c r="F30" t="n">
         <v>10</v>
       </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
@@ -1099,6 +1195,9 @@
       <c r="F31" t="n">
         <v>10</v>
       </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
@@ -1120,6 +1219,9 @@
       <c r="F32" t="n">
         <v>10</v>
       </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
@@ -1141,6 +1243,9 @@
       <c r="F33" t="n">
         <v>10</v>
       </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
@@ -1162,6 +1267,9 @@
       <c r="F34" t="n">
         <v>10</v>
       </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
@@ -1183,6 +1291,9 @@
       <c r="F35" t="n">
         <v>10</v>
       </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
@@ -1203,6 +1314,201 @@
       </c>
       <c r="F36" t="n">
         <v>10</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>118</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>safe_idle</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>companion.bark.safe_idle.t2.1</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>119</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>safe_idle</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>companion.bark.safe_idle.t2.2</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>120</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>safe_idle</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>companion.bark.safe_idle.t2.3</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>121</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>safe_idle</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>companion.bark.safe_idle.t3.1</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>122</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>safe_idle</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>companion.bark.safe_idle.t3.2</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>123</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>safe_idle</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>companion.bark.safe_idle.t3.3</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>124</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gift_receive</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>companion.bark.gift_receive.1</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>125</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gift_receive</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>companion.bark.gift_receive.2</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
